--- a/specification/Nhom11_FZP1_Fuzzing_Spec.xlsx
+++ b/specification/Nhom11_FZP1_Fuzzing_Spec.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ThongTin" sheetId="1" state="visible" r:id="rId1"/>
@@ -19,14 +18,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TestCase" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,28 +33,16 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -63,35 +50,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00D9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="00D9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="00D9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00D9D9D9"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -455,7 +425,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="12" customWidth="1" style="1" min="1" max="1"/>
+    <col width="44.33203125" customWidth="1" style="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -470,26 +444,26 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>fzp1_binary_parser</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="3" ht="57.6" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Bộ phân tích cú pháp file nhị phân FZP1 phục vụ kiểm thử Fuzzing và kiểm chứng hình thức</t>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Bộ phân tích cú pháp gói tin nhị phân FZP1 (Magic 4B, Length 1B, Payload, Checksum XOR 1B) phục vụ kiểm thử Fuzzing và kiểm chứng an toàn bộ nhớ.</t>
         </is>
       </c>
     </row>
@@ -504,8 +478,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="12" customWidth="1" style="1" min="1" max="1"/>
+    <col width="18" customWidth="1" style="1" min="2" max="2"/>
+    <col width="26.44140625" customWidth="1" style="1" min="3" max="6"/>
+    <col width="13" customWidth="1" style="1" min="7" max="7"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -544,313 +524,224 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TC-FZ-01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>REQ-FZ-01, REQ-FZ-02</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Kiểm chứng xung đột giữa giải mã Magic và Checksum</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+    <row r="2" ht="72" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>TC-1</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>REQ-1, REQ-2</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Tranh chấp trạng thái xác thực Magic và Checksum</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>Hệ thống ở trạng thái 'st_idle'</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>1. Luồng phân tích nạp magic header
-2. Luồng kiểm tra checksum nạp tệp
-3. Kiểm tra công thức CTL</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>Kiểm chứng mô hình Kripke 4 trạng thái sinh từ đặc tả</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>AG(!violation) ĐÚNG và không có trạng thái deadlock</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TC-FZ-02</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>REQ-FZ-03, CON-FZ-02</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Kiểm thử lỗi tràn bộ đệm stack khi payload_len &gt; 16 byte</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Hàm parse_fzp1_payload() sinh từ đặc tả</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>1. Nạp tệp FZP1 có payload_len=24 byte
-2. Thực thi hàm sao chép strcpy
-3. Quan sát vi phạm ô nhớ</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Phát hiện cảnh báo dangerous-function (CWE-121 Stack Buffer Overflow)</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+    <row r="3" ht="43.2" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>TC-2</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>REQ-3</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Payload FZP1 vượt quá 16 byte gây tràn stack</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Hàm parse_fzp1_payload() sinh từ đặc tả (bug=buffer-overflow)</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Sinh mã C cho parse_fzp1_payload()
+Chạy kiểm tra AST C</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Phát hiện nguy cơ buffer-overflow (CWE-120/121)</t>
+        </is>
+      </c>
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TC-FZ-03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>REQ-FZ-04, REQ-FZ-05, REQ-FZ-06</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Kiểm tra chu kỳ cấp phát và giải phóng tài nguyên heap</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Các hàm alloc_fzp1_cache, close_fzp1_session, release_fzp1_stream</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1. Gộp toàn bộ mã C của các hàm quản lý tài nguyên
-2. Chạy bộ phân tích bộ nhớ tĩnh Memory Analyzer
-3. Kiểm tra vòng đời con trỏ</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Phát hiện đủ 3 lớp lỗ hổng bộ nhớ: Rò rỉ (CWE-401), Free 2 lần (CWE-415), UAF (CWE-416)</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+    <row r="4" ht="57.6" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>TC-3</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>REQ-4, REQ-5, REQ-6</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Kiểm tra vòng đời bộ nhớ của cache/session</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>write_fzp1_cache(), close_fzp1_session(), release_fzp1_stream() đã sinh</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Kiểm tra mã C của cả 3 hàm quản lý heap</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Phát hiện đủ 3 loại lỗi: memory-leak (CWE-401), double-free (CWE-415), use-after-free (CWE-416)</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TC-FZ-04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>REQ-FZ-07</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Kiểm chứng nguy cơ tràn số nguyên 32-bit trên bộ đếm byte</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Hai biến header_bytes và payload_bytes &gt;= 0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1. Thiết lập ràng buộc SMT Z3 Bit-Vector 32-bit
-2. Thực thi hàm check_int32_overflow()
-3. Trích xuất nghiệm SAT</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Z3 Solver trả về kết quả SAT cùng nghiệm minh chứng nguy cơ tràn số nguyên</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+    <row r="5" ht="43.2" customHeight="1">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>TC-4</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>REQ-7</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Bộ tích lũy byte fzp1_byte_accumulator vượt giới hạn int32</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>header_bytes, payload_bytes &gt;= 0 và tổng &gt; 2,000,000,000</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Chạy check_int32_overflow() bằng Z3 trên biểu thức header_bytes + payload_bytes</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Kết quả SAT (phát hiện nguy cơ tràn số CWE-190)</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TC-FZ-05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>REQ-FZ-08</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Fuzzing hộp đen hàm tính tỷ lệ tệp hợp lệ</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Hàm Python calculate_fzp1_ratio(valid_files, total_files)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1. Chạy blackbox_fuzz() ngẫu nhiên 300 lượt
-2. Sinh ngẫu nhiên tham số đầu vào
-3. Kiểm tra ngoại lệ ZeroDivisionError</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Tìm thấy ít nhất 1 đầu vào có total_files=0 kích hoạt ZeroDivisionError</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+    <row r="6" ht="28.8" customHeight="1">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>TC-5</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>REQ-8</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Chia tỷ lệ gói tin fzp1_ratio với mẫu số bằng 0</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>Hàm fzp1_ratio(issued, consumed) sinh từ đặc tả</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Chạy blackbox_fuzz() 300 lần</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Tìm được ít nhất 1 crash ZeroDivisionError (CWE-369)</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TC-FZ-06</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>REQ-FZ-09, CON-FZ-03</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Kiểm thử Concolic giải ngược cặp token mở khóa khẩn cấp</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Hàm Python verify_fzp1_unlock_token(token_a, token_b)</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1. Thu thập điều kiện nhánh qua Symbolic Execution
-2. Chạy concolic_fuzz() với Z3 SMT Solver
-3. Trích xuất cặp nghiệm thỏa mãn</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Thuật toán Concolic giải hệ phương trình tìm ra token_a=18010, token_b=20529 sau 1 bước</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TC-FZ-07</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>NFR-FZ-01, NFR-FZ-02, CON-FZ-01</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Kiểm định thông lượng phân tích tệp nhị phân FZP1</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Tập dữ liệu kiểm thử 1000 tệp nhị phân chuẩn</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1. Nạp tập seed corpus 1000 tệp FZP1
-2. Đo thời gian phân tích và kiểm tra checksum
-3. Tính toán thông lượng trung bình</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Hệ thống đạt thông lượng &gt;= 1000 tệp/s (NFR-FZ-01) và thời gian phản hồi &lt; 2ms (NFR-FZ-02)</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TC-FZ-08</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>NFR-FZ-04, CON-FZ-04, CON-FZ-05</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Kiểm tra mức tiêu thụ RAM và biên dịch theo chuẩn C99</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Môi trường thực thi parser biên dịch bằng Clang -O2</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1. Biên dịch mã nguồn với -std=c99 -Wall -Wextra
-2. Nạp tệp nhị phân có kích thước cực đại 256 byte
-3. Giám sát dung lượng RAM tiêu thụ</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Dung lượng RAM tiêu thụ không vượt quá 32KB (NFR-FZ-04) và mã nguồn biên dịch sạch cảnh báo</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+    <row r="7" ht="57.6" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>TC-6</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>REQ-9</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Tìm cặp mã mở khóa khẩn cấp fzp1_unlock_token bằng concolic fuzzing</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>Hàm fzp1_unlock_token(token_a, token_b), magic=(18010, 20529)</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>Chạy concolic_fuzz() với Z3 SMT Solver</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>Tìm được đúng bộ giá trị (18010, 20529) trong 1 lần thử</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -868,7 +759,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="12" customWidth="1" style="1" min="1" max="1"/>
+    <col width="37" customWidth="1" style="1" min="2" max="2"/>
+    <col width="12" customWidth="1" style="1" min="3" max="3"/>
+    <col width="13" customWidth="1" style="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -892,199 +789,199 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>REQ-FZ-01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Hệ thống phải xác thực chính xác 4 byte Magic Number "FZP1" ở đầu tệp nhị phân trước khi giải mã</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+    <row r="2" ht="43.2" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>REQ-1</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Hệ thống phải xác thực chính xác 4 byte Magic Number "FZP1" ở đầu gói tin trước khi xử lý</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>safety</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>REQ-FZ-02</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Bộ phân tích cú pháp FZP1 không được rơi vào bế tắc (deadlock-free) trong mọi chu trình xử lý tệp</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+    <row r="3" ht="28.8" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>REQ-2</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Bộ phân tích cú pháp FZP1 không được rơi vào deadlock trong mọi chu trình xử lý gói tin</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>liveness</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>REQ-FZ-03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Hàm parse_fzp1_payload() khi giải mã payload phải sao chép an toàn vào bộ đệm stack cố định 16 byte</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+    <row r="4" ht="28.8" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>REQ-3</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Hàm parse_fzp1_payload() không được gây tràn bộ đệm stack (CWE-121) khi kích thước payload vượt quá 16 byte</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>memory</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>REQ-FZ-04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Bộ đệm tệp nhị phân cấp phát trên heap phải được giải phóng đúng sau khi phân tích hoàn tất</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+    <row r="5" ht="28.8" customHeight="1">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>REQ-4</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Vùng đệm tệp nhị phân cấp phát trên heap phải được giải phóng đúng sau khi hoàn tất xử lý (CWE-401)</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>memory</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>REQ-FZ-05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Hàm đóng phiên giải mã tệp không được giải phóng bộ nhớ hai lần (CWE-415 double-free)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+    <row r="6" ht="28.8" customHeight="1">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>REQ-5</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Hàm đóng phiên xử lý gói tin không được giải phóng cùng một con trỏ nhiều hơn 1 lần (CWE-415 double-free)</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>memory</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>REQ-FZ-06</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Con trỏ bộ đệm sau khi giải phóng không được tái sử dụng (CWE-416 use-after-free)</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+    <row r="7" ht="43.2" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>REQ-6</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Sau khi giải phóng tài nguyên vùng nhớ, hệ thống không được tiếp tục truy cập con trỏ đó (CWE-416 use-after-free)</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>memory</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>REQ-FZ-07</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Bộ tích lũy dung lượng byte đã xử lý không được vượt giới hạn tràn số nguyên 32-bit (CWE-190)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+    <row r="8" ht="28.8" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>REQ-7</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>Bộ tích lũy dung lượng byte dữ liệu fzp1_byte_accumulator không được tràn kiểu int 32-bit (CWE-190)</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
         <is>
           <t>safety</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>REQ-FZ-08</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Hàm tính toán tỷ lệ tệp hợp lệ calculate_fzp1_ratio() không được gây lỗi chia cho không</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+    <row r="9" ht="28.8" customHeight="1">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>REQ-8</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>Hàm tính tỷ lệ gói tin hợp lệ fzp1_ratio không được gây lỗi chia cho không (CWE-369)</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
         <is>
           <t>functional</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>REQ-FZ-09</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Cơ chế xác thực khóa bí mật verify_fzp1_unlock_token() phải kiểm tra chính xác cặp token 16-bit</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+    <row r="10" ht="57.6" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>REQ-9</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>Cơ chế xác thực token mở khóa khẩn cấp fzp1_unlock_token cần được kiểm thử bằng kỹ thuật concolic fuzzing SMT Z3</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
         <is>
           <t>functional</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="1" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1101,8 +998,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="12" customWidth="1" style="1" min="1" max="1"/>
+    <col width="34" customWidth="1" style="1" min="2" max="2"/>
+    <col width="13" customWidth="1" style="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1121,88 +1023,54 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>NFR-FZ-01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Bộ parser FZP1 phải đạt thông lượng xử lý tối thiểu 1000 tệp nhị phân mỗi giây trên CPU thử nghiệm</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+    <row r="2" ht="43.2" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>NFR-1</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Bộ parser FZP1 phải xử lý tối thiểu 500 gói tin/giây trên môi trường thử nghiệm</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>NFR-FZ-02</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Thời gian phân tích hợp lệ và kiểm tra checksum mỗi tệp trung bình dưới 2ms</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+    <row r="3" ht="28.8" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>NFR-2</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Thời gian phản hồi trung bình cho một gói tin phải dưới 50ms</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>NFR-FZ-03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Nhật ký kiểm toán giải mã tệp nhị phân phải được ghi đồng bộ nguyên tử không làm mất log</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+    <row r="4" ht="43.2" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>NFR-3</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Nhật ký giải mã gói tin phải được ghi đồng bộ (không mất dữ liệu) kể cả khi tiến trình bị ngắt</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>NFR-FZ-04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Mức tiêu thụ bộ nhớ RAM tối đa của bộ parser FZP1 không vượt quá 32KB</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>NFR-FZ-05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Tỷ lệ lỗi không xác định (unhandled exceptions) trong quá trình fuzzing phải là 0%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>LOW</t>
         </is>
       </c>
     </row>
@@ -1217,8 +1085,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="12" customWidth="1" style="1" min="1" max="1"/>
+    <col width="33.5546875" customWidth="1" style="1" min="2" max="2"/>
+    <col width="13" customWidth="1" style="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1237,86 +1110,52 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CON-FZ-01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Tệp nhị phân phải tuân thủ nghiêm ngặt cấu trúc FZP1: 4B Magic | 1B Length | N-B Payload | 1B XOR Checksum</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+    <row r="2" ht="43.2" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>CON-1</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Gói tin FZP1 tuân thủ cấu trúc nhị phân: 4B Magic | 1B Length | N-B Payload | 1B XOR Checksum</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>CON-2</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Bộ đệm stack frame cục bộ nhận payload có kích thước cố định 16 byte</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CON-FZ-02</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Vùng đệm xử lý payload cục bộ trên stack frame có kích thước cố định 16 byte (Buffer_Size = 16)</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CON-FZ-03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Mã mở khóa khẩn cấp FZP1 phải là cặp số nguyên 16-bit dương cố định</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CON-FZ-04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Tổng chiều dài toàn bộ tệp nhị phân đầu vào không được vượt quá 256 byte</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CON-FZ-05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Toàn bộ mã nguồn C xử lý phân tích cú pháp FZP1 phải biên dịch sạch theo chuẩn ISO C99</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+    <row r="4" ht="28.8" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>CON-3</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Cặp mã mở khóa khẩn cấp thiết bị FZP1 phải là cặp số nguyên 16-bit dương</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -1334,101 +1173,107 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="29.5546875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>TrangThai</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>KhoiTao</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nhan</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>ChuyenDenCacTrangThai</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>st_idle</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>safe, ready</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>st_magic_valid, st_checksum_valid</t>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>safe</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>st_magic_ok, st_checksum_ok</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>st_magic_valid</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>st_magic_ok</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
         <is>
           <t>magic_ok</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>st_idle, st_overflow_hazard</t>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>st_idle, st_conflict</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>st_checksum_valid</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>st_checksum_ok</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
         <is>
           <t>checksum_ok</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>st_idle</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>st_overflow_hazard</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>st_conflict</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
         <is>
           <t>magic_ok, checksum_ok, violation</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>st_idle</t>
         </is>
@@ -1445,48 +1290,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>CongThucCTL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>AG(!violation)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>EF(magic_ok)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>EF(checksum_ok)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>EF(violation)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>AF(safe)</t>
         </is>
       </c>
     </row>
@@ -1502,27 +1329,30 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>MenhDe1</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>MenhDe2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>magic_ok</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>checksum_ok</t>
         </is>
@@ -1540,265 +1370,286 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="22.88671875" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="15.77734375" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="16.77734375" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Ten</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>NgonNgu</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Loai</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>ThamSo</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>KichThuocBuffer</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Loi</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>GiaTriBiMat1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>GiaTriBiMat2</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>parse_fzp1_payload</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>buffer_copy</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>raw_payload</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>buffer-overflow</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>1234</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>5678</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>alloc_fzp1_cache</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>write_fzp1_cache</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>alloc_release</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr"/>
-      <c r="E3" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>memory-leak</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>1234</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>5678</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>close_fzp1_session</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>alloc_release</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>double-free</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>1234</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>5678</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>release_fzp1_stream</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>alloc_release</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>use-after-free</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>1234</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>5678</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>calculate_fzp1_ratio</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>fzp1_ratio</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>divide</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>valid_files, total_files</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>issued, consumed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>1234</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>5678</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>verify_fzp1_unlock_token</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>fzp1_unlock_token</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>python</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>magic_value</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>token_a, token_b</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>18010</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>20529</t>
         </is>
@@ -1815,138 +1666,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="23.5546875" customWidth="1" min="1" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Ten</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>BienSoNguyen</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>DieuKien</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>BieuThucTran</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>fzp1_checksum_accumulator</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>header_sum, payload_sum</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>header_sum &gt;= 0 and payload_sum &gt;= 0 and header_sum &lt;= 32767 and payload_sum &lt;= 32767</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>header_sum + payload_sum</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>fzp1_file_counter</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>rx_files, tx_files</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>rx_files &gt;= 0 and tx_files &gt;= 0 and rx_files &lt;= 65535 and tx_files &lt;= 65535</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>rx_files + tx_files</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>fzp1_byte_accumulator</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>header_bytes, payload_bytes</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>header_bytes &gt;= 0 and payload_bytes &gt;= 0 and header_bytes &lt;= 2147483647 and payload_bytes &lt;= 2147483647</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>header_bytes &gt;= 0 and payload_bytes &gt;= 0 and header_bytes + payload_bytes &gt; 2000000000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>header_bytes + payload_bytes</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>fzp1_duration_timer</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>parse_time_ms, verify_time_ms</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>parse_time_ms &gt;= 0 and verify_time_ms &gt;= 0 and parse_time_ms &lt;= 65535 and verify_time_ms &lt;= 65535</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>parse_time_ms + verify_time_ms</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>fzp1_drop_counter</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>corrupt_magic_drops, bad_checksum_drops</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>corrupt_magic_drops &gt;= 0 and bad_checksum_drops &gt;= 0 and corrupt_magic_drops &lt;= 32767 and bad_checksum_drops &lt;= 32767</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>corrupt_magic_drops + bad_checksum_drops</t>
         </is>
       </c>
     </row>

--- a/specification/Nhom11_FZP1_Fuzzing_Spec.xlsx
+++ b/specification/Nhom11_FZP1_Fuzzing_Spec.xlsx
@@ -998,7 +998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="1" min="1" max="1"/>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Thời gian phản hồi trung bình cho một gói tin phải dưới 50ms</t>
+          <t>Thời gian phản hồi trung bình cho một gói tin nhị phân phải dưới 50ms</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
@@ -1071,6 +1071,40 @@
       <c r="C4" s="1" t="inlineStr">
         <is>
           <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>NFR-4</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Dung lượng bộ nhớ RAM tiêu thụ tối đa của tiến trình parser không vượt quá 2MB</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>NFR-5</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Tỷ lệ thất thoát gói tin (packet drop rate) khi tiếp nhận luồng dữ liệu liên tục không quá 0.01%</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" style="1" min="1" max="1"/>
@@ -1158,6 +1192,40 @@
       <c r="C4" s="1" t="inlineStr">
         <is>
           <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>CON-4</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Độ dài dữ liệu trường payload len được quy định bởi số nguyên không dấu uint8_t (0 đến 255)</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>CON-5</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Toàn bộ tài nguyên heap cấp phát cho buffer tệp tin phải được giải phóng run-to-completion</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1314,6 +1382,27 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>EF(magic_ok)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EF(checksum_ok)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>EF(violation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AF(safe)</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="2"/>
@@ -1355,6 +1444,54 @@
       <c r="B2" t="inlineStr">
         <is>
           <t>checksum_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>safe</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>violation</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>safe</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>magic_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>safe</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>checksum_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>magic_ok</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>violation</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="23.5546875" customWidth="1" min="1" max="4"/>
@@ -1716,6 +1853,94 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>fzp1_packet_counter</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>daily_pkts, burst_pkts</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>daily_pkts &gt;= 0 and burst_pkts &gt;= 0 and daily_pkts + burst_pkts &gt; 32767</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>daily_pkts + burst_pkts</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>fzp1_session_id</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>base_id, offset_id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>base_id &gt;= 0 and offset_id &gt;= 0 and base_id + offset_id &gt; 65535</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>base_id + offset_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>fzp1_crc_accumulator</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>crc_part1, crc_part2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>crc_part1 &gt;= 0 and crc_part2 &gt;= 0 and crc_part1 + crc_part2 &gt; 2000000000</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>crc_part1 + crc_part2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>fzp1_total_stream_bytes</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>stream_in, stream_out</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>stream_in &gt;= 0 and stream_out &gt;= 0 and stream_in + stream_out &gt; 2000000000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>stream_in + stream_out</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/specification/Nhom11_FZP1_Fuzzing_Spec.xlsx
+++ b/specification/Nhom11_FZP1_Fuzzing_Spec.xlsx
@@ -1417,7 +1417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="2"/>
@@ -1444,54 +1444,6 @@
       <c r="B2" t="inlineStr">
         <is>
           <t>checksum_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>safe</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>violation</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>safe</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>magic_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>safe</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>checksum_ok</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>magic_ok</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>violation</t>
         </is>
       </c>
     </row>

--- a/specification/Nhom11_FZP1_Fuzzing_Spec.xlsx
+++ b/specification/Nhom11_FZP1_Fuzzing_Spec.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Bộ phân tích cú pháp gói tin nhị phân FZP1 (Magic 4B, Length 1B, Payload, Checksum XOR 1B) phục vụ kiểm thử Fuzzing và kiểm chứng an toàn bộ nhớ.</t>
+          <t>Bộ phân tích cú pháp gói tin nhị phân FZP1 (Magic 4B, Length 4B uint32, Payload, Checksum XOR 1B) phục vụ kiểm thử Fuzzing và kiểm chứng an toàn bộ nhớ.</t>
         </is>
       </c>
     </row>
@@ -552,7 +552,7 @@
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>AG(!violation) ĐÚNG và không có trạng thái deadlock</t>
+          <t>AG(!violation) VI PHẠM (phát hiện nguy cơ vi phạm an toàn tại st_conflict), EF(violation) ĐÚNG, và hệ thống không có deadlock</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
@@ -607,27 +607,27 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>REQ-4, REQ-5, REQ-6</t>
+          <t>REQ-4, REQ-5</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>Kiểm tra vòng đời bộ nhớ của cache/session</t>
+          <t>Hủy phiên sớm gây giải phóng kép (CWE-415)</t>
         </is>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>write_fzp1_cache(), close_fzp1_session(), release_fzp1_stream() đã sinh</t>
+          <t>Hàm close_fzp1_session() dọn dẹp bộ đệm session trên heap</t>
         </is>
       </c>
       <c r="E4" s="1" t="inlineStr">
         <is>
-          <t>Kiểm tra mã C của cả 3 hàm quản lý heap</t>
+          <t>Kích hoạt mã điều khiển CMD 0xFF (CMD_ABORT_SESSION) trên v0 và v1</t>
         </is>
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>Phát hiện đủ 3 loại lỗi: memory-leak (CWE-401), double-free (CWE-415), use-after-free (CWE-416)</t>
+          <t>v0 crash Double-Free (0xC0000374 / ASan), v1 gán NULL idempotent an toàn (CERT MEM30-C, MEM31-C)</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
@@ -644,32 +644,32 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>REQ-7</t>
+          <t>REQ-6</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>Bộ tích lũy byte fzp1_byte_accumulator vượt giới hạn int32</t>
+          <t>Tái lập luồng stream gây con trỏ lơ lửng Use-After-Free (CWE-416)</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>header_bytes, payload_bytes &gt;= 0 và tổng &gt; 2,000,000,000</t>
+          <t>Hàm release_fzp1_stream() xử lý luồng sự kiện stream</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
-          <t>Chạy check_int32_overflow() bằng Z3 trên biểu thức header_bytes + payload_bytes</t>
+          <t>Kích hoạt mã điều khiển CMD 0xFE (CMD_RESET_STREAM) trên v0 và v1</t>
         </is>
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>Kết quả SAT (phát hiện nguy cơ tràn số CWE-190)</t>
+          <t>v0 crash Heap Use-After-Free (0xC0000005 / shadow [fd]), v1 gọi callback trước khi free và xóa con trỏ (CERT MEM30-C)</t>
         </is>
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>Bộ tích lũy dung lượng byte dữ liệu fzp1_byte_accumulator không được tràn kiểu int 32-bit (CWE-190)</t>
+          <t>Kiểm soát an toàn trường length uint32 và kích thước tổng gói tin theo hạn mức giao thức, ngăn chặn wrap tràn số (CERT STR31-C, INT31-C)</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Gói tin FZP1 tuân thủ cấu trúc nhị phân: 4B Magic | 1B Length | N-B Payload | 1B XOR Checksum</t>
+          <t>Gói tin FZP1 tuân thủ cấu trúc nhị phân: 4B Magic | 4B Length | N-B Payload | 1B XOR Checksum</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Độ dài dữ liệu trường payload len được quy định bởi số nguyên không dấu uint8_t (0 đến 255)</t>
+          <t>Độ dài dữ liệu trường payload len được quy định bởi số nguyên không dấu 4-byte uint32_t (0 đến 2^32-1)</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>safe</t>
+          <t>safe, session_closed</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1302,7 +1302,7 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
-          <t>magic_ok</t>
+          <t>magic_ok, header_valid</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>checksum_ok</t>
+          <t>checksum_ok, session_active</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="2"/>
@@ -1444,6 +1444,54 @@
       <c r="B2" t="inlineStr">
         <is>
           <t>checksum_ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>violation</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>safe</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>session_active</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>session_closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>header_valid</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>violation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>checksum_ok</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>violation</t>
         </is>
       </c>
     </row>
